--- a/3.2. Example, working.xlsx
+++ b/3.2. Example, working.xlsx
@@ -97,7 +97,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1,657</t>
+    <t xml:space="preserve">1,638</t>
   </si>
   <si>
     <t xml:space="preserve">Sex of respondent
@@ -808,40 +808,40 @@
         <v>17</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>93.8</v>
+        <v>88.9</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>94.3</v>
+        <v>89.5</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>93.5</v>
+        <v>88.4</v>
       </c>
       <c r="G6" s="18" t="n">
         <v>85.1</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>88.8</v>
+        <v>88.3</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>82.2</v>
+        <v>82.6</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>78.5</v>
+        <v>84.3</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>75.9</v>
+        <v>84.8</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>81</v>
+        <v>83.9</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>77</v>
+        <v>83.5</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>84</v>
+        <v>78.4</v>
       </c>
     </row>
     <row r="7">
@@ -852,40 +852,40 @@
         <v>17</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="E7" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <v>3.3</v>
       </c>
-      <c r="F7" s="19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="I7" s="19" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>3.7</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0.5</v>
@@ -905,31 +905,31 @@
         <v>1.2</v>
       </c>
       <c r="G8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="18" t="n">
         <v>2.4</v>
       </c>
-      <c r="H8" s="18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L8" s="18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M8" s="18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N8" s="18" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -940,40 +940,40 @@
         <v>17</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="10">
@@ -984,40 +984,40 @@
         <v>17</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="L10" s="18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="M10" s="18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N10" s="18" t="n">
         <v>5</v>
       </c>
       <c r="O10" s="18" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1028,40 +1028,40 @@
         <v>17</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="19" t="n">
         <v>2.1</v>
       </c>
-      <c r="J11" s="19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M11" s="19" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N11" s="19" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1081,31 +1081,31 @@
         <v>0.4</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>2.6</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -1204,40 +1204,40 @@
         <v>16</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="N15" s="20" t="n">
         <v>139</v>
       </c>
       <c r="O15" s="20" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
@@ -1370,13 +1370,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>84.9</v>
+        <v>85</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>84.3</v>
+        <v>87</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>85.4</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="6">
@@ -1387,13 +1387,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="7">
@@ -1404,13 +1404,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -1421,13 +1421,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="9">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -1455,13 +1455,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -1472,13 +1472,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
@@ -1526,10 +1526,10 @@
         <v>24</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15">

--- a/3.2. Example, working.xlsx
+++ b/3.2. Example, working.xlsx
@@ -240,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -257,12 +257,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -283,30 +283,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -625,50 +601,50 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="NA" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -684,35 +660,35 @@
       <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="19.5" customHeight="1">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -725,38 +701,38 @@
       <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="L4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="O4" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="NA" customHeight="1">
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -769,38 +745,38 @@
       <c r="E5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
@@ -813,38 +789,38 @@
       <c r="E6" s="12" t="n">
         <v>89.5</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="12" t="n">
         <v>88.4</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="12" t="n">
         <v>85.1</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="12" t="n">
         <v>88.3</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="12" t="n">
         <v>82.6</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="12" t="n">
         <v>84.3</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K6" s="12" t="n">
         <v>84.8</v>
       </c>
-      <c r="L6" s="18" t="n">
+      <c r="L6" s="12" t="n">
         <v>83.9</v>
       </c>
-      <c r="M6" s="18" t="n">
+      <c r="M6" s="12" t="n">
         <v>80.5</v>
       </c>
-      <c r="N6" s="18" t="n">
+      <c r="N6" s="12" t="n">
         <v>83.5</v>
       </c>
-      <c r="O6" s="18" t="n">
+      <c r="O6" s="12" t="n">
         <v>78.4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -857,38 +833,38 @@
       <c r="E7" s="13" t="n">
         <v>5.5</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="13" t="n">
         <v>4.2</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="13" t="n">
         <v>4.6</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="13" t="n">
         <v>3.3</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="13" t="n">
         <v>5.7</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="13" t="n">
         <v>5.1</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="13" t="n">
         <v>3.8</v>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="L7" s="13" t="n">
         <v>6.3</v>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="M7" s="13" t="n">
         <v>6.3</v>
       </c>
-      <c r="N7" s="19" t="n">
+      <c r="N7" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="13" t="n">
         <v>9.8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19.5" customHeight="1">
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
@@ -901,38 +877,38 @@
       <c r="E8" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="12" t="n">
         <v>1.7</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K8" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="L8" s="18" t="n">
+      <c r="L8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="18" t="n">
+      <c r="M8" s="12" t="n">
         <v>2.4</v>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="N8" s="12" t="n">
         <v>3.6</v>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="O8" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
@@ -945,38 +921,38 @@
       <c r="E9" s="13" t="n">
         <v>2.3</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="13" t="n">
         <v>4.2</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="13" t="n">
         <v>3.2</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="13" t="n">
         <v>3.9</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="13" t="n">
         <v>2.3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="13" t="n">
         <v>3.3</v>
       </c>
-      <c r="L9" s="19" t="n">
+      <c r="L9" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="M9" s="19" t="n">
+      <c r="M9" s="13" t="n">
         <v>3.6</v>
       </c>
-      <c r="N9" s="19" t="n">
+      <c r="N9" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="O9" s="19" t="n">
+      <c r="O9" s="13" t="n">
         <v>4.6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
@@ -989,38 +965,38 @@
       <c r="E10" s="12" t="n">
         <v>1.8</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="12" t="n">
         <v>3.4</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="12" t="n">
         <v>2.8</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="K10" s="12" t="n">
         <v>2.2</v>
       </c>
-      <c r="L10" s="18" t="n">
+      <c r="L10" s="12" t="n">
         <v>3.4</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="12" t="n">
         <v>2.7</v>
       </c>
-      <c r="N10" s="18" t="n">
+      <c r="N10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="O10" s="12" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
@@ -1033,38 +1009,38 @@
       <c r="E11" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="n">
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
         <v>2.4</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="13" t="n">
         <v>3.9</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="L11" s="19" t="n">
+      <c r="L11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="19" t="n">
+      <c r="M11" s="13" t="n">
         <v>2.1</v>
       </c>
-      <c r="N11" s="19" t="n">
+      <c r="N11" s="13" t="n">
         <v>3.6</v>
       </c>
-      <c r="O11" s="19" t="n">
+      <c r="O11" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19.5" customHeight="1">
       <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1077,127 +1053,127 @@
       <c r="E12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="I12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18" t="n">
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="12" t="n">
         <v>2.2</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L12" s="12" t="n">
         <v>2.9</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="M12" s="12" t="n">
         <v>2.4</v>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="N12" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="O12" s="12" t="n">
         <v>3.6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="6" t="s">
+    <row r="13" ht="NA" customHeight="1">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="O13" s="20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="s">
+      <c r="C13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="NA" customHeight="1">
+      <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="6" t="s">
+      <c r="C14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="NA" customHeight="1">
+      <c r="B15" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="14" t="s">
@@ -1209,38 +1185,38 @@
       <c r="E15" s="14" t="n">
         <v>219</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="14" t="n">
         <v>259</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="14" t="n">
         <v>410</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="14" t="n">
         <v>180</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="14" t="n">
         <v>230</v>
       </c>
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="14" t="n">
         <v>389</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="K15" s="14" t="n">
         <v>184</v>
       </c>
-      <c r="L15" s="20" t="n">
+      <c r="L15" s="14" t="n">
         <v>205</v>
       </c>
-      <c r="M15" s="20" t="n">
+      <c r="M15" s="14" t="n">
         <v>333</v>
       </c>
-      <c r="N15" s="20" t="n">
+      <c r="N15" s="14" t="n">
         <v>139</v>
       </c>
-      <c r="O15" s="20" t="n">
+      <c r="O15" s="14" t="n">
         <v>194</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="B16" s="8" t="s">
         <v>13</v>
       </c>
@@ -1312,23 +1288,23 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="19.5" customHeight="1">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1341,11 +1317,11 @@
       <c r="E3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="NA" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1358,11 +1334,11 @@
       <c r="E4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1375,11 +1351,11 @@
       <c r="E5" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="12" t="n">
         <v>83.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="19.5" customHeight="1">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1392,11 +1368,11 @@
       <c r="E6" s="13" t="n">
         <v>3.7</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="13" t="n">
         <v>6.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1409,11 +1385,11 @@
       <c r="E7" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="12" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19.5" customHeight="1">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1426,11 +1402,11 @@
       <c r="E8" s="13" t="n">
         <v>2.4</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="13" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
@@ -1443,11 +1419,11 @@
       <c r="E9" s="12" t="n">
         <v>2.8</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="12" t="n">
         <v>2.3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1460,11 +1436,11 @@
       <c r="E10" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="13" t="n">
         <v>1.6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -1477,46 +1453,46 @@
       <c r="E11" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="12" t="n">
         <v>1.6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="6" t="s">
+    <row r="12" ht="NA" customHeight="1">
+      <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="s">
+      <c r="C12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="NA" customHeight="1">
+      <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="6" t="s">
+      <c r="C13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="NA" customHeight="1">
+      <c r="B14" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="14" t="s">
@@ -1528,11 +1504,11 @@
       <c r="E14" s="14" t="n">
         <v>737</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="14" t="n">
         <v>901</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19.5" customHeight="1">
       <c r="B15" s="8" t="s">
         <v>13</v>
       </c>
